--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thryv-my.sharepoint.com/personal/tr993n_thryv_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B947117-7746-4485-A568-75FD5005C36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D54F154-01D2-2443-ADDB-F5A34911949F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31485" yWindow="2685" windowWidth="21600" windowHeight="11175" xr2:uid="{187D6435-4C4C-4876-857B-D6DFE1A49DEF}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{187D6435-4C4C-4876-857B-D6DFE1A49DEF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1191,33 +1191,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AFB7ADC-FA70-4DA6-8B12-A8E6E2100754}">
   <dimension ref="A1:AQ65"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.7109375" customWidth="1"/>
-    <col min="2" max="2" width="33.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" customWidth="1"/>
-    <col min="8" max="8" width="7" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" customWidth="1"/>
-    <col min="10" max="11" width="9.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.42578125" customWidth="1"/>
-    <col min="13" max="13" width="8.7109375" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="8.140625" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
-    <col min="17" max="17" width="8.85546875" customWidth="1"/>
-    <col min="18" max="18" width="7.28515625" customWidth="1"/>
+    <col min="1" max="1" width="37.6640625" customWidth="1"/>
+    <col min="2" max="2" width="33.5" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" customWidth="1"/>
+    <col min="6" max="6" width="0" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="7" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5" hidden="1" customWidth="1"/>
+    <col min="10" max="11" width="9.5" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="6.83203125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="8.1640625" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="9" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="8.83203125" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="7.33203125" hidden="1" customWidth="1"/>
     <col min="19" max="30" width="0" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="7" customWidth="1"/>
-    <col min="32" max="32" width="7.140625" customWidth="1"/>
-    <col min="33" max="33" width="9.85546875" customWidth="1"/>
-    <col min="34" max="34" width="8.42578125" customWidth="1"/>
-    <col min="35" max="35" width="7.140625" customWidth="1"/>
-    <col min="36" max="36" width="8.42578125" customWidth="1"/>
-    <col min="37" max="37" width="9.140625" customWidth="1"/>
+    <col min="31" max="31" width="7" hidden="1" customWidth="1"/>
+    <col min="32" max="32" width="7.1640625" customWidth="1"/>
+    <col min="33" max="33" width="9.83203125" customWidth="1"/>
+    <col min="34" max="34" width="8.5" customWidth="1"/>
+    <col min="35" max="35" width="7.1640625" customWidth="1"/>
+    <col min="36" max="36" width="8.5" customWidth="1"/>
+    <col min="37" max="37" width="9.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1348,7 +1349,7 @@
         <v>46382</v>
       </c>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>8</v>
       </c>
@@ -1463,13 +1464,15 @@
       <c r="AL2" s="25">
         <v>45</v>
       </c>
-      <c r="AM2" s="25"/>
+      <c r="AM2" s="25">
+        <v>32</v>
+      </c>
       <c r="AN2" s="25"/>
       <c r="AO2" s="25"/>
       <c r="AP2" s="25"/>
       <c r="AQ2" s="25"/>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>8</v>
       </c>
@@ -1584,13 +1587,15 @@
       <c r="AL3" s="25">
         <v>411</v>
       </c>
-      <c r="AM3" s="25"/>
+      <c r="AM3" s="25">
+        <v>461</v>
+      </c>
       <c r="AN3" s="25"/>
       <c r="AO3" s="25"/>
       <c r="AP3" s="25"/>
       <c r="AQ3" s="25"/>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A4" s="15" t="s">
         <v>8</v>
       </c>
@@ -1705,13 +1710,15 @@
       <c r="AL4" s="25">
         <v>5</v>
       </c>
-      <c r="AM4" s="25"/>
+      <c r="AM4" s="25">
+        <v>5</v>
+      </c>
       <c r="AN4" s="25"/>
       <c r="AO4" s="25"/>
       <c r="AP4" s="25"/>
       <c r="AQ4" s="25"/>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>8</v>
       </c>
@@ -1826,13 +1833,15 @@
       <c r="AL5" s="25">
         <v>95</v>
       </c>
-      <c r="AM5" s="25"/>
+      <c r="AM5" s="25">
+        <v>62</v>
+      </c>
       <c r="AN5" s="25"/>
       <c r="AO5" s="25"/>
       <c r="AP5" s="25"/>
       <c r="AQ5" s="25"/>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A6" s="26" t="s">
         <v>14</v>
       </c>
@@ -1947,13 +1956,15 @@
       <c r="AL6" s="35">
         <v>556</v>
       </c>
-      <c r="AM6" s="35"/>
+      <c r="AM6" s="35">
+        <v>560</v>
+      </c>
       <c r="AN6" s="35"/>
       <c r="AO6" s="35"/>
       <c r="AP6" s="35"/>
       <c r="AQ6" s="35"/>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
@@ -2068,13 +2079,15 @@
       <c r="AL7" s="25">
         <v>0</v>
       </c>
-      <c r="AM7" s="25"/>
+      <c r="AM7" s="25">
+        <v>5</v>
+      </c>
       <c r="AN7" s="25"/>
       <c r="AO7" s="25"/>
       <c r="AP7" s="25"/>
       <c r="AQ7" s="25"/>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A8" s="15" t="s">
         <v>8</v>
       </c>
@@ -2189,13 +2202,15 @@
       <c r="AL8" s="25">
         <v>189</v>
       </c>
-      <c r="AM8" s="25"/>
+      <c r="AM8" s="25">
+        <v>253</v>
+      </c>
       <c r="AN8" s="25"/>
       <c r="AO8" s="25"/>
       <c r="AP8" s="25"/>
       <c r="AQ8" s="25"/>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A9" s="15" t="s">
         <v>8</v>
       </c>
@@ -2310,13 +2325,15 @@
       <c r="AL9" s="25">
         <v>0</v>
       </c>
-      <c r="AM9" s="25"/>
+      <c r="AM9" s="25">
+        <v>0</v>
+      </c>
       <c r="AN9" s="25"/>
       <c r="AO9" s="25"/>
       <c r="AP9" s="25"/>
       <c r="AQ9" s="25"/>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A10" s="15" t="s">
         <v>19</v>
       </c>
@@ -2431,13 +2448,15 @@
       <c r="AL10" s="25">
         <v>16</v>
       </c>
-      <c r="AM10" s="25"/>
+      <c r="AM10" s="25">
+        <v>12</v>
+      </c>
       <c r="AN10" s="25"/>
       <c r="AO10" s="25"/>
       <c r="AP10" s="25"/>
       <c r="AQ10" s="25"/>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="15" t="s">
         <v>21</v>
       </c>
@@ -2552,13 +2571,15 @@
       <c r="AL11" s="25">
         <v>31</v>
       </c>
-      <c r="AM11" s="25"/>
+      <c r="AM11" s="25">
+        <v>28</v>
+      </c>
       <c r="AN11" s="25"/>
       <c r="AO11" s="25"/>
       <c r="AP11" s="25"/>
       <c r="AQ11" s="25"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="15" t="s">
         <v>22</v>
       </c>
@@ -2673,13 +2694,15 @@
       <c r="AL12" s="25">
         <v>0</v>
       </c>
-      <c r="AM12" s="25"/>
+      <c r="AM12" s="25">
+        <v>0</v>
+      </c>
       <c r="AN12" s="25"/>
       <c r="AO12" s="25"/>
       <c r="AP12" s="25"/>
       <c r="AQ12" s="25"/>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="15" t="s">
         <v>24</v>
       </c>
@@ -2794,13 +2817,15 @@
       <c r="AL13" s="25">
         <v>0</v>
       </c>
-      <c r="AM13" s="25"/>
+      <c r="AM13" s="25">
+        <v>0</v>
+      </c>
       <c r="AN13" s="25"/>
       <c r="AO13" s="25"/>
       <c r="AP13" s="25"/>
       <c r="AQ13" s="25"/>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="15" t="s">
         <v>26</v>
       </c>
@@ -2915,13 +2940,15 @@
       <c r="AL14" s="25">
         <v>0</v>
       </c>
-      <c r="AM14" s="25"/>
+      <c r="AM14" s="25">
+        <v>0</v>
+      </c>
       <c r="AN14" s="25"/>
       <c r="AO14" s="25"/>
       <c r="AP14" s="25"/>
       <c r="AQ14" s="25"/>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
         <v>28</v>
       </c>
@@ -3036,13 +3063,15 @@
       <c r="AL15" s="25">
         <v>0</v>
       </c>
-      <c r="AM15" s="25"/>
+      <c r="AM15" s="25">
+        <v>0</v>
+      </c>
       <c r="AN15" s="25"/>
       <c r="AO15" s="25"/>
       <c r="AP15" s="25"/>
       <c r="AQ15" s="25"/>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="15" t="s">
         <v>30</v>
       </c>
@@ -3157,13 +3186,15 @@
       <c r="AL16" s="25">
         <v>0</v>
       </c>
-      <c r="AM16" s="25"/>
+      <c r="AM16" s="25">
+        <v>0</v>
+      </c>
       <c r="AN16" s="25"/>
       <c r="AO16" s="25"/>
       <c r="AP16" s="25"/>
       <c r="AQ16" s="25"/>
     </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="15" t="s">
         <v>31</v>
       </c>
@@ -3278,13 +3309,15 @@
       <c r="AL17" s="25">
         <v>0</v>
       </c>
-      <c r="AM17" s="25"/>
+      <c r="AM17" s="25">
+        <v>0</v>
+      </c>
       <c r="AN17" s="25"/>
       <c r="AO17" s="25"/>
       <c r="AP17" s="25"/>
       <c r="AQ17" s="25"/>
     </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="15" t="s">
         <v>32</v>
       </c>
@@ -3399,13 +3432,15 @@
       <c r="AL18" s="25">
         <v>0</v>
       </c>
-      <c r="AM18" s="25"/>
+      <c r="AM18" s="25">
+        <v>0</v>
+      </c>
       <c r="AN18" s="25"/>
       <c r="AO18" s="25"/>
       <c r="AP18" s="25"/>
       <c r="AQ18" s="25"/>
     </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>33</v>
       </c>
@@ -3520,13 +3555,15 @@
       <c r="AL19" s="25">
         <v>0</v>
       </c>
-      <c r="AM19" s="25"/>
+      <c r="AM19" s="25">
+        <v>0</v>
+      </c>
       <c r="AN19" s="25"/>
       <c r="AO19" s="25"/>
       <c r="AP19" s="25"/>
       <c r="AQ19" s="25"/>
     </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>35</v>
       </c>
@@ -3641,13 +3678,15 @@
       <c r="AL20" s="25">
         <v>3</v>
       </c>
-      <c r="AM20" s="25"/>
+      <c r="AM20" s="25">
+        <v>4</v>
+      </c>
       <c r="AN20" s="25"/>
       <c r="AO20" s="25"/>
       <c r="AP20" s="25"/>
       <c r="AQ20" s="25"/>
     </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="15" t="s">
         <v>37</v>
       </c>
@@ -3762,13 +3801,15 @@
       <c r="AL21" s="25">
         <v>0</v>
       </c>
-      <c r="AM21" s="25"/>
+      <c r="AM21" s="25">
+        <v>0</v>
+      </c>
       <c r="AN21" s="25"/>
       <c r="AO21" s="25"/>
       <c r="AP21" s="25"/>
       <c r="AQ21" s="25"/>
     </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>39</v>
       </c>
@@ -3883,13 +3924,15 @@
       <c r="AL22" s="25">
         <v>0</v>
       </c>
-      <c r="AM22" s="25"/>
+      <c r="AM22" s="25">
+        <v>0</v>
+      </c>
       <c r="AN22" s="25"/>
       <c r="AO22" s="25"/>
       <c r="AP22" s="25"/>
       <c r="AQ22" s="25"/>
     </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="15" t="s">
         <v>41</v>
       </c>
@@ -3960,13 +4003,15 @@
       <c r="AL23" s="25">
         <v>0</v>
       </c>
-      <c r="AM23" s="25"/>
+      <c r="AM23" s="25">
+        <v>50</v>
+      </c>
       <c r="AN23" s="25"/>
       <c r="AO23" s="25"/>
       <c r="AP23" s="25"/>
       <c r="AQ23" s="25"/>
     </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="40" t="s">
         <v>43</v>
       </c>
@@ -4081,13 +4126,15 @@
       <c r="AL24" s="25">
         <v>22</v>
       </c>
-      <c r="AM24" s="25"/>
+      <c r="AM24" s="25">
+        <v>6</v>
+      </c>
       <c r="AN24" s="25"/>
       <c r="AO24" s="25"/>
       <c r="AP24" s="25"/>
       <c r="AQ24" s="25"/>
     </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="42" t="s">
         <v>45</v>
       </c>
@@ -4200,13 +4247,15 @@
       <c r="AL25" s="35">
         <v>1373</v>
       </c>
-      <c r="AM25" s="35"/>
+      <c r="AM25" s="35">
+        <v>1478</v>
+      </c>
       <c r="AN25" s="35"/>
       <c r="AO25" s="35"/>
       <c r="AP25" s="35"/>
       <c r="AQ25" s="35"/>
     </row>
-    <row r="26" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" hidden="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
         <v>46</v>
       </c>
@@ -4319,7 +4368,7 @@
       <c r="AP26" s="25"/>
       <c r="AQ26" s="25"/>
     </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A27" s="60" t="s">
         <v>48</v>
       </c>
@@ -4366,7 +4415,7 @@
       <c r="AP27" s="60"/>
       <c r="AQ27" s="60"/>
     </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>49</v>
       </c>
@@ -4481,13 +4530,15 @@
       <c r="AL28" s="25">
         <v>63</v>
       </c>
-      <c r="AM28" s="25"/>
+      <c r="AM28" s="25">
+        <v>53</v>
+      </c>
       <c r="AN28" s="25"/>
       <c r="AO28" s="25"/>
       <c r="AP28" s="25"/>
       <c r="AQ28" s="25"/>
     </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A29" s="15" t="s">
         <v>51</v>
       </c>
@@ -4602,13 +4653,15 @@
       <c r="AL29" s="25">
         <v>0</v>
       </c>
-      <c r="AM29" s="25"/>
+      <c r="AM29" s="25">
+        <v>0</v>
+      </c>
       <c r="AN29" s="25"/>
       <c r="AO29" s="25"/>
       <c r="AP29" s="25"/>
       <c r="AQ29" s="25"/>
     </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A30" s="15" t="s">
         <v>53</v>
       </c>
@@ -4723,13 +4776,15 @@
       <c r="AL30" s="25">
         <v>0</v>
       </c>
-      <c r="AM30" s="25"/>
+      <c r="AM30" s="25">
+        <v>0</v>
+      </c>
       <c r="AN30" s="25"/>
       <c r="AO30" s="25"/>
       <c r="AP30" s="25"/>
       <c r="AQ30" s="25"/>
     </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A31" s="15" t="s">
         <v>55</v>
       </c>
@@ -4844,13 +4899,15 @@
       <c r="AL31" s="25">
         <v>0</v>
       </c>
-      <c r="AM31" s="25"/>
+      <c r="AM31" s="25">
+        <v>0</v>
+      </c>
       <c r="AN31" s="25"/>
       <c r="AO31" s="25"/>
       <c r="AP31" s="25"/>
       <c r="AQ31" s="25"/>
     </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A32" s="15" t="s">
         <v>57</v>
       </c>
@@ -4965,13 +5022,15 @@
       <c r="AL32" s="25">
         <v>0</v>
       </c>
-      <c r="AM32" s="25"/>
+      <c r="AM32" s="25">
+        <v>0</v>
+      </c>
       <c r="AN32" s="25"/>
       <c r="AO32" s="25"/>
       <c r="AP32" s="25"/>
       <c r="AQ32" s="25"/>
     </row>
-    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A33" s="15" t="s">
         <v>59</v>
       </c>
@@ -5086,13 +5145,15 @@
       <c r="AL33" s="25">
         <v>0</v>
       </c>
-      <c r="AM33" s="25"/>
+      <c r="AM33" s="25">
+        <v>0</v>
+      </c>
       <c r="AN33" s="25"/>
       <c r="AO33" s="25"/>
       <c r="AP33" s="25"/>
       <c r="AQ33" s="25"/>
     </row>
-    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A34" s="15" t="s">
         <v>61</v>
       </c>
@@ -5205,13 +5266,15 @@
       <c r="AL34" s="25">
         <v>0</v>
       </c>
-      <c r="AM34" s="25"/>
+      <c r="AM34" s="25">
+        <v>0</v>
+      </c>
       <c r="AN34" s="25"/>
       <c r="AO34" s="25"/>
       <c r="AP34" s="25"/>
       <c r="AQ34" s="25"/>
     </row>
-    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A35" s="15" t="s">
         <v>63</v>
       </c>
@@ -5326,13 +5389,15 @@
       <c r="AL35" s="25">
         <v>6</v>
       </c>
-      <c r="AM35" s="25"/>
+      <c r="AM35" s="25">
+        <v>0</v>
+      </c>
       <c r="AN35" s="25"/>
       <c r="AO35" s="25"/>
       <c r="AP35" s="25"/>
       <c r="AQ35" s="25"/>
     </row>
-    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A36" s="15" t="s">
         <v>65</v>
       </c>
@@ -5447,13 +5512,15 @@
       <c r="AL36" s="25">
         <v>0</v>
       </c>
-      <c r="AM36" s="25"/>
+      <c r="AM36" s="25">
+        <v>0</v>
+      </c>
       <c r="AN36" s="25"/>
       <c r="AO36" s="25"/>
       <c r="AP36" s="25"/>
       <c r="AQ36" s="25"/>
     </row>
-    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A37" s="15" t="s">
         <v>67</v>
       </c>
@@ -5568,13 +5635,15 @@
       <c r="AL37" s="25">
         <v>0</v>
       </c>
-      <c r="AM37" s="25"/>
+      <c r="AM37" s="25">
+        <v>0</v>
+      </c>
       <c r="AN37" s="25"/>
       <c r="AO37" s="25"/>
       <c r="AP37" s="25"/>
       <c r="AQ37" s="25"/>
     </row>
-    <row r="38" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A38" s="47" t="s">
         <v>69</v>
       </c>
@@ -5689,13 +5758,15 @@
       <c r="AL38" s="25">
         <v>0</v>
       </c>
-      <c r="AM38" s="25"/>
+      <c r="AM38" s="25">
+        <v>0</v>
+      </c>
       <c r="AN38" s="25"/>
       <c r="AO38" s="25"/>
       <c r="AP38" s="25"/>
       <c r="AQ38" s="25"/>
     </row>
-    <row r="39" spans="1:43" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:43" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="15" t="s">
         <v>71</v>
       </c>
@@ -5810,13 +5881,15 @@
       <c r="AL39" s="25">
         <v>0</v>
       </c>
-      <c r="AM39" s="25"/>
+      <c r="AM39" s="25">
+        <v>0</v>
+      </c>
       <c r="AN39" s="25"/>
       <c r="AO39" s="25"/>
       <c r="AP39" s="25"/>
       <c r="AQ39" s="25"/>
     </row>
-    <row r="40" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A40" s="40" t="s">
         <v>73</v>
       </c>
@@ -5931,13 +6004,15 @@
       <c r="AL40" s="25">
         <v>29</v>
       </c>
-      <c r="AM40" s="25"/>
+      <c r="AM40" s="25">
+        <v>25</v>
+      </c>
       <c r="AN40" s="25"/>
       <c r="AO40" s="25"/>
       <c r="AP40" s="25"/>
       <c r="AQ40" s="25"/>
     </row>
-    <row r="41" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A41" s="42" t="s">
         <v>75</v>
       </c>
@@ -6050,13 +6125,15 @@
       <c r="AL41" s="35">
         <v>98</v>
       </c>
-      <c r="AM41" s="35"/>
+      <c r="AM41" s="35">
+        <v>78</v>
+      </c>
       <c r="AN41" s="35"/>
       <c r="AO41" s="35"/>
       <c r="AP41" s="35"/>
       <c r="AQ41" s="35"/>
     </row>
-    <row r="42" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A42" s="15" t="s">
         <v>76</v>
       </c>
@@ -6171,13 +6248,15 @@
       <c r="AL42" s="25">
         <v>49</v>
       </c>
-      <c r="AM42" s="25"/>
+      <c r="AM42" s="25">
+        <v>57</v>
+      </c>
       <c r="AN42" s="25"/>
       <c r="AO42" s="25"/>
       <c r="AP42" s="25"/>
       <c r="AQ42" s="25"/>
     </row>
-    <row r="43" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A43" s="15" t="s">
         <v>78</v>
       </c>
@@ -6292,13 +6371,15 @@
       <c r="AL43" s="25">
         <v>37</v>
       </c>
-      <c r="AM43" s="25"/>
+      <c r="AM43" s="25">
+        <v>43</v>
+      </c>
       <c r="AN43" s="25"/>
       <c r="AO43" s="25"/>
       <c r="AP43" s="25"/>
       <c r="AQ43" s="25"/>
     </row>
-    <row r="44" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A44" s="15" t="s">
         <v>80</v>
       </c>
@@ -6413,13 +6494,15 @@
       <c r="AL44" s="25">
         <v>5</v>
       </c>
-      <c r="AM44" s="25"/>
+      <c r="AM44" s="25">
+        <v>4</v>
+      </c>
       <c r="AN44" s="25"/>
       <c r="AO44" s="25"/>
       <c r="AP44" s="25"/>
       <c r="AQ44" s="25"/>
     </row>
-    <row r="45" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A45" s="15" t="s">
         <v>82</v>
       </c>
@@ -6534,13 +6617,15 @@
       <c r="AL45" s="25">
         <v>3</v>
       </c>
-      <c r="AM45" s="25"/>
+      <c r="AM45" s="25">
+        <v>2</v>
+      </c>
       <c r="AN45" s="25"/>
       <c r="AO45" s="25"/>
       <c r="AP45" s="25"/>
       <c r="AQ45" s="25"/>
     </row>
-    <row r="46" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A46" s="15" t="s">
         <v>84</v>
       </c>
@@ -6655,13 +6740,15 @@
       <c r="AL46" s="25">
         <v>1</v>
       </c>
-      <c r="AM46" s="25"/>
+      <c r="AM46" s="25">
+        <v>2</v>
+      </c>
       <c r="AN46" s="25"/>
       <c r="AO46" s="25"/>
       <c r="AP46" s="25"/>
       <c r="AQ46" s="25"/>
     </row>
-    <row r="47" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A47" s="15" t="s">
         <v>86</v>
       </c>
@@ -6776,13 +6863,15 @@
       <c r="AL47" s="25">
         <v>1</v>
       </c>
-      <c r="AM47" s="25"/>
+      <c r="AM47" s="25">
+        <v>1</v>
+      </c>
       <c r="AN47" s="25"/>
       <c r="AO47" s="25"/>
       <c r="AP47" s="25"/>
       <c r="AQ47" s="25"/>
     </row>
-    <row r="48" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
         <v>88</v>
       </c>
@@ -6897,13 +6986,15 @@
       <c r="AL48" s="25">
         <v>0</v>
       </c>
-      <c r="AM48" s="25"/>
+      <c r="AM48" s="25">
+        <v>1</v>
+      </c>
       <c r="AN48" s="25"/>
       <c r="AO48" s="25"/>
       <c r="AP48" s="25"/>
       <c r="AQ48" s="25"/>
     </row>
-    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
         <v>90</v>
       </c>
@@ -7018,13 +7109,15 @@
       <c r="AL49" s="25">
         <v>0</v>
       </c>
-      <c r="AM49" s="25"/>
+      <c r="AM49" s="25">
+        <v>1</v>
+      </c>
       <c r="AN49" s="25"/>
       <c r="AO49" s="25"/>
       <c r="AP49" s="25"/>
       <c r="AQ49" s="25"/>
     </row>
-    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A50" s="15" t="s">
         <v>92</v>
       </c>
@@ -7139,13 +7232,15 @@
       <c r="AL50" s="25">
         <v>0</v>
       </c>
-      <c r="AM50" s="25"/>
+      <c r="AM50" s="25">
+        <v>0</v>
+      </c>
       <c r="AN50" s="25"/>
       <c r="AO50" s="25"/>
       <c r="AP50" s="25"/>
       <c r="AQ50" s="25"/>
     </row>
-    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A51" s="15" t="s">
         <v>94</v>
       </c>
@@ -7260,13 +7355,15 @@
       <c r="AL51" s="25">
         <v>0</v>
       </c>
-      <c r="AM51" s="25"/>
+      <c r="AM51" s="25">
+        <v>0</v>
+      </c>
       <c r="AN51" s="25"/>
       <c r="AO51" s="25"/>
       <c r="AP51" s="25"/>
       <c r="AQ51" s="25"/>
     </row>
-    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A52" s="15" t="s">
         <v>96</v>
       </c>
@@ -7381,13 +7478,15 @@
       <c r="AL52" s="25">
         <v>0</v>
       </c>
-      <c r="AM52" s="25"/>
+      <c r="AM52" s="25">
+        <v>1</v>
+      </c>
       <c r="AN52" s="25"/>
       <c r="AO52" s="25"/>
       <c r="AP52" s="25"/>
       <c r="AQ52" s="25"/>
     </row>
-    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A53" s="15" t="s">
         <v>98</v>
       </c>
@@ -7502,13 +7601,15 @@
       <c r="AL53" s="25">
         <v>1</v>
       </c>
-      <c r="AM53" s="25"/>
+      <c r="AM53" s="25">
+        <v>0</v>
+      </c>
       <c r="AN53" s="25"/>
       <c r="AO53" s="25"/>
       <c r="AP53" s="25"/>
       <c r="AQ53" s="25"/>
     </row>
-    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A54" s="15" t="s">
         <v>100</v>
       </c>
@@ -7623,13 +7724,15 @@
       <c r="AL54" s="25">
         <v>0</v>
       </c>
-      <c r="AM54" s="25"/>
+      <c r="AM54" s="25">
+        <v>0</v>
+      </c>
       <c r="AN54" s="25"/>
       <c r="AO54" s="25"/>
       <c r="AP54" s="25"/>
       <c r="AQ54" s="25"/>
     </row>
-    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A55" s="15" t="s">
         <v>102</v>
       </c>
@@ -7744,13 +7847,15 @@
       <c r="AL55" s="25">
         <v>0</v>
       </c>
-      <c r="AM55" s="25"/>
+      <c r="AM55" s="25">
+        <v>0</v>
+      </c>
       <c r="AN55" s="25"/>
       <c r="AO55" s="25"/>
       <c r="AP55" s="25"/>
       <c r="AQ55" s="25"/>
     </row>
-    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A56" s="15" t="s">
         <v>104</v>
       </c>
@@ -7865,13 +7970,15 @@
       <c r="AL56" s="25">
         <v>0</v>
       </c>
-      <c r="AM56" s="25"/>
+      <c r="AM56" s="25">
+        <v>0</v>
+      </c>
       <c r="AN56" s="25"/>
       <c r="AO56" s="25"/>
       <c r="AP56" s="25"/>
       <c r="AQ56" s="25"/>
     </row>
-    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A57" s="15" t="s">
         <v>106</v>
       </c>
@@ -7986,13 +8093,15 @@
       <c r="AL57" s="25">
         <v>0</v>
       </c>
-      <c r="AM57" s="25"/>
+      <c r="AM57" s="25">
+        <v>0</v>
+      </c>
       <c r="AN57" s="25"/>
       <c r="AO57" s="25"/>
       <c r="AP57" s="25"/>
       <c r="AQ57" s="25"/>
     </row>
-    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
         <v>108</v>
       </c>
@@ -8107,13 +8216,15 @@
       <c r="AL58" s="25">
         <v>9</v>
       </c>
-      <c r="AM58" s="25"/>
+      <c r="AM58" s="25">
+        <v>5</v>
+      </c>
       <c r="AN58" s="25"/>
       <c r="AO58" s="25"/>
       <c r="AP58" s="25"/>
       <c r="AQ58" s="25"/>
     </row>
-    <row r="59" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="15" t="s">
         <v>110</v>
       </c>
@@ -8228,13 +8339,15 @@
       <c r="AL59" s="25">
         <v>3</v>
       </c>
-      <c r="AM59" s="25"/>
+      <c r="AM59" s="25">
+        <v>6</v>
+      </c>
       <c r="AN59" s="25"/>
       <c r="AO59" s="25"/>
       <c r="AP59" s="25"/>
       <c r="AQ59" s="25"/>
     </row>
-    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A60" s="21" t="s">
         <v>112</v>
       </c>
@@ -8349,13 +8462,15 @@
       <c r="AL60" s="25">
         <v>1</v>
       </c>
-      <c r="AM60" s="25"/>
+      <c r="AM60" s="25">
+        <v>1</v>
+      </c>
       <c r="AN60" s="25"/>
       <c r="AO60" s="25"/>
       <c r="AP60" s="25"/>
       <c r="AQ60" s="25"/>
     </row>
-    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A61" s="21" t="s">
         <v>114</v>
       </c>
@@ -8470,13 +8585,15 @@
       <c r="AL61" s="25">
         <v>0</v>
       </c>
-      <c r="AM61" s="25"/>
+      <c r="AM61" s="25">
+        <v>0</v>
+      </c>
       <c r="AN61" s="25"/>
       <c r="AO61" s="25"/>
       <c r="AP61" s="25"/>
       <c r="AQ61" s="25"/>
     </row>
-    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A62" s="21" t="s">
         <v>116</v>
       </c>
@@ -8591,13 +8708,15 @@
       <c r="AL62" s="25">
         <v>4</v>
       </c>
-      <c r="AM62" s="25"/>
+      <c r="AM62" s="25">
+        <v>10</v>
+      </c>
       <c r="AN62" s="25"/>
       <c r="AO62" s="25"/>
       <c r="AP62" s="25"/>
       <c r="AQ62" s="25"/>
     </row>
-    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A63" s="21" t="s">
         <v>118</v>
       </c>
@@ -8688,13 +8807,15 @@
       <c r="AL63" s="25">
         <v>6</v>
       </c>
-      <c r="AM63" s="25"/>
+      <c r="AM63" s="25">
+        <v>1</v>
+      </c>
       <c r="AN63" s="25"/>
       <c r="AO63" s="25"/>
       <c r="AP63" s="25"/>
       <c r="AQ63" s="25"/>
     </row>
-    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A64" s="47" t="s">
         <v>119</v>
       </c>
@@ -8773,13 +8894,15 @@
       <c r="AL64" s="25">
         <v>69</v>
       </c>
-      <c r="AM64" s="25"/>
+      <c r="AM64" s="25">
+        <v>83</v>
+      </c>
       <c r="AN64" s="25"/>
       <c r="AO64" s="25"/>
       <c r="AP64" s="25"/>
       <c r="AQ64" s="25"/>
     </row>
-    <row r="65" spans="1:43" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A65" s="15" t="s">
         <v>121</v>
       </c>
@@ -8858,7 +8981,9 @@
       <c r="AL65" s="25">
         <v>51</v>
       </c>
-      <c r="AM65" s="25"/>
+      <c r="AM65" s="25">
+        <v>54</v>
+      </c>
       <c r="AN65" s="25"/>
       <c r="AO65" s="25"/>
       <c r="AP65" s="25"/>
